--- a/excel/CharacterData.xlsx
+++ b/excel/CharacterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE06E5CB-F584-C148-B8FE-EE628B13F2AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8955EF-7BF0-C844-9D1F-DB8724E9B83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -136,11 +136,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>리피</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>character_leafy_pie</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>리피파이</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -539,10 +539,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="13"/>

--- a/excel/CharacterData.xlsx
+++ b/excel/CharacterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8955EF-7BF0-C844-9D1F-DB8724E9B83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A58C05-557D-E543-B74A-5F5570D28EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -141,6 +141,39 @@
   </si>
   <si>
     <t>리피파이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미카</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>미카</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_mika</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -252,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -264,6 +297,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -545,7 +580,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13"/>
+    <row r="6" spans="1:5" ht="15">
+      <c r="A6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="7" spans="1:5" ht="13"/>
     <row r="12" spans="1:5" ht="13">
       <c r="E12" s="1"/>

--- a/excel/CharacterData.xlsx
+++ b/excel/CharacterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A58C05-557D-E543-B74A-5F5570D28EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2477B3-7D55-D24B-9EC1-721F15DE7635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,10 +74,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>character_saturn</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>[</t>
     </r>
@@ -162,6 +158,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>]</t>
@@ -174,6 +171,10 @@
   </si>
   <si>
     <t>character_mika</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_player</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -285,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -298,7 +299,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -555,40 +555,40 @@
         <v>7</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="13"/>
